--- a/testdata/configurationUAT/data.xlsx
+++ b/testdata/configurationUAT/data.xlsx
@@ -1,397 +1,345 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15240" windowHeight="12330"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
-  <si>
-    <t>PIN</t>
-  </si>
-  <si>
-    <t>wrong_pin</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>mobile_number</t>
-  </si>
-  <si>
-    <t>mobile_number_hidden</t>
-  </si>
-  <si>
-    <t>my_account</t>
-  </si>
-  <si>
-    <t>account_iban</t>
-  </si>
-  <si>
-    <t>account_username</t>
-  </si>
-  <si>
-    <t>account_address</t>
-  </si>
-  <si>
-    <t>account_address_profile</t>
-  </si>
-  <si>
-    <t>account_address_payment_preview</t>
-  </si>
-  <si>
-    <t>account_address_format_upcoming_standing_order</t>
-  </si>
-  <si>
-    <t>account_username_currency</t>
-  </si>
-  <si>
-    <t>basic_contact</t>
-  </si>
-  <si>
-    <t>basic_contact_iban</t>
-  </si>
-  <si>
-    <t>basic_contact_address</t>
-  </si>
-  <si>
-    <t>my_account_other</t>
-  </si>
-  <si>
-    <t>my_account_other_iban</t>
-  </si>
-  <si>
-    <t>my_account_other_address</t>
-  </si>
-  <si>
-    <t>my_account_var_name</t>
-  </si>
-  <si>
-    <t>my_account_var_iban</t>
-  </si>
-  <si>
-    <t>auth_account_var_name</t>
-  </si>
-  <si>
-    <t>auth_account_var_username</t>
-  </si>
-  <si>
-    <t>auth_account_var_username_reverse</t>
-  </si>
-  <si>
-    <t>auth_account_var_iban</t>
-  </si>
-  <si>
-    <t>my_account_var_pos_name</t>
-  </si>
-  <si>
-    <t>my_account_var_pos_iban</t>
-  </si>
-  <si>
-    <t>another_bank_inside_slovenia_name</t>
-  </si>
-  <si>
-    <t>another_bank_inside_slovenia_iban</t>
-  </si>
-  <si>
-    <t>contact_to_add_iban</t>
-  </si>
-  <si>
-    <t>contact_for_edit</t>
-  </si>
-  <si>
-    <t>edited_contact_info</t>
-  </si>
-  <si>
-    <t>auth_account_iban</t>
-  </si>
-  <si>
-    <t>auth_account_iban_no_space</t>
-  </si>
-  <si>
-    <t>auth_account_username</t>
-  </si>
-  <si>
-    <t>auth_account_name</t>
-  </si>
-  <si>
-    <t>auth_account_address</t>
-  </si>
-  <si>
-    <t>my_account_deposit_name</t>
-  </si>
-  <si>
-    <t>my_account_deposit_iban</t>
-  </si>
-  <si>
-    <t>my_account_kredit_name</t>
-  </si>
-  <si>
-    <t>my_account_kredit_iban</t>
-  </si>
-  <si>
-    <t>my_account_second_vr_name</t>
-  </si>
-  <si>
-    <t>my_account_second_vr_iban</t>
-  </si>
-  <si>
-    <t>humanitarian_iban</t>
-  </si>
-  <si>
-    <t>humanitarian_name</t>
-  </si>
-  <si>
-    <t>united_kingdom_iban</t>
-  </si>
-  <si>
-    <t>united_kingdom_name</t>
-  </si>
-  <si>
-    <t>united_kingdom_address</t>
-  </si>
-  <si>
-    <t>bosnia_iban</t>
-  </si>
-  <si>
-    <t>address_for_foreign_pregled_to</t>
-  </si>
-  <si>
-    <t>address_for_foreign_pregled_to_bank</t>
-  </si>
-  <si>
-    <t>filePath</t>
-  </si>
-  <si>
-    <t>chf_account_iban</t>
-  </si>
-  <si>
-    <t>croatia_iban</t>
-  </si>
-  <si>
-    <t>serbia_iban</t>
-  </si>
-  <si>
-    <t>auth_pos_var_account_name</t>
-  </si>
-  <si>
-    <t>auth_pos_var_account_iban</t>
-  </si>
-  <si>
-    <t>unauth_pos_var_iban</t>
-  </si>
-  <si>
-    <t>unauth_var_iban</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>envName</t>
-  </si>
-  <si>
-    <t>LUKA.SAJEVIC@NLB.SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+420 72 148 24 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">+386 40 *** 012 </t>
-  </si>
-  <si>
-    <t>Paket Aktivni</t>
-  </si>
-  <si>
-    <t>SI56 0230 5402 0800 314</t>
-  </si>
-  <si>
-    <t>SAJEVIC LUKA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULICA NIKOLA TESLA 16   ,
-1230 DOMŽALE,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULICA NIKOLA TESLA 16,
-1230 DOMŽALE
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULICA NIKOLA TESLA 16,
-DOMŽALE,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULICA NIKOLA TESLA 16,
-1230    DOMŽALE,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t>LUKA SAJEVIC</t>
-  </si>
-  <si>
-    <t>ADAM</t>
-  </si>
-  <si>
-    <t>SI56 0228 5485 2979 814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEST,
-TEST,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t>NLB Varčevalni račun mladih</t>
-  </si>
-  <si>
-    <t>SI56 0230 3396 4338 167</t>
-  </si>
-  <si>
-    <t>NLB Varčevalni račun (UROŠ HVASTIJA)</t>
-  </si>
-  <si>
-    <t>HVASTIJA UROŠ</t>
-  </si>
-  <si>
-    <t>UROŠ HVASTIJA</t>
-  </si>
-  <si>
-    <t>SI56 0206 0122 0460 343</t>
-  </si>
-  <si>
-    <t>NLB Postopno varčevanje</t>
-  </si>
-  <si>
-    <t>SI56 0230 1392 9722 457</t>
-  </si>
-  <si>
-    <t>ENERGETIKA LJUBLJANA, D.O.O.</t>
-  </si>
-  <si>
-    <t>SI56 0292 4025 3764 022</t>
-  </si>
-  <si>
-    <t>SI56 0206 0121 9105 641</t>
-  </si>
-  <si>
-    <t>TEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TESTADRESSEDIT,
-TESTCITYEDIT,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t>SI56 0223 6145 1777 416</t>
-  </si>
-  <si>
-    <t>SI56022361451777416</t>
-  </si>
-  <si>
-    <t>KALAPČIEV VANI</t>
-  </si>
-  <si>
-    <t>Paket Premium (VANI KALAPČIEV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMINJANSKA CESTA 93,
-PORTOROŽ - PORTOROSE,
-SLOVENIA                           </t>
-  </si>
-  <si>
-    <t>NLB Depozit</t>
-  </si>
-  <si>
-    <t>SI56 0230 1392 9722 554</t>
-  </si>
-  <si>
-    <t>Hitri kredit</t>
-  </si>
-  <si>
-    <t>SI56 0230 0388 4348 719</t>
-  </si>
-  <si>
-    <t>SI56 0310 0111 1122 296</t>
-  </si>
-  <si>
-    <t>RDEČI KRIŽ SLOVENIJE - ZVEZA ZDRUŽE</t>
-  </si>
-  <si>
-    <t>GB68 BARC 2087 9493 7713 26</t>
-  </si>
-  <si>
-    <t>GBCONTACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEST,
-TEST,
-UNITED KINGDOM                     </t>
-  </si>
-  <si>
-    <t>BA39 5620 9981 6539 5407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEST21,
-TEST12,
-BOSNIA AND HERZEGOVINA             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEST31,
-TEST51,
-BOSNIA AND HERZEGOVINA             </t>
-  </si>
-  <si>
-    <t>pooblastilo_2023-08-22t09-57-07.158z.pdf</t>
-  </si>
-  <si>
-    <t>CH21 0077 7008 8884 4457 9</t>
-  </si>
-  <si>
-    <t>HR63 2484 0081 1065 4708 5</t>
-  </si>
-  <si>
-    <t>RS35 3106 8307 0000 4044 51</t>
-  </si>
-  <si>
-    <t>NLB Postopno varčevanje (DBP ART 01)</t>
-  </si>
-  <si>
-    <t>SI56 0223 3144 2828 052</t>
-  </si>
-  <si>
-    <t>SI56 0230 1392 9722 845</t>
-  </si>
-  <si>
-    <t>SI56 0201 9347 0417 316</t>
-  </si>
-  <si>
-    <t>#after</t>
-  </si>
-  <si>
-    <t>UAT</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="100">
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>webpage</t>
+  </si>
+  <si>
+    <t>isMock</t>
+  </si>
+  <si>
+    <t>currentEnv</t>
+  </si>
+  <si>
+    <t>term_deposit_number</t>
+  </si>
+  <si>
+    <t>term_deposit_name</t>
+  </si>
+  <si>
+    <t>term_deposit_number2</t>
+  </si>
+  <si>
+    <t>term_deposit_name2</t>
+  </si>
+  <si>
+    <t>term_deposit_number3</t>
+  </si>
+  <si>
+    <t>term_deposit_name3</t>
+  </si>
+  <si>
+    <t>term_deposit_account_details_opening_date</t>
+  </si>
+  <si>
+    <t>term_deposit_account_details_expiration_date</t>
+  </si>
+  <si>
+    <t>maturity_account</t>
+  </si>
+  <si>
+    <t>currentDomesticAccountName</t>
+  </si>
+  <si>
+    <t>currentDomesticAccountBBAN</t>
+  </si>
+  <si>
+    <t>second_personal_account_name</t>
+  </si>
+  <si>
+    <t>second_personal_account_bban</t>
+  </si>
+  <si>
+    <t>bad_current_domestic_account_number</t>
+  </si>
+  <si>
+    <t>personal_account_iban</t>
+  </si>
+  <si>
+    <t>personal_account_name</t>
+  </si>
+  <si>
+    <t>second_personal_account_iban</t>
+  </si>
+  <si>
+    <t>saving_account_number</t>
+  </si>
+  <si>
+    <t>saving_account_name</t>
+  </si>
+  <si>
+    <t>saving_account_number2</t>
+  </si>
+  <si>
+    <t>saving_account_name2</t>
+  </si>
+  <si>
+    <t>search_purpose</t>
+  </si>
+  <si>
+    <t>credit_card_name</t>
+  </si>
+  <si>
+    <t>credit_card_number</t>
+  </si>
+  <si>
+    <t>credit_card_2_name</t>
+  </si>
+  <si>
+    <t>credit_card_2_number</t>
+  </si>
+  <si>
+    <t>loan_account_number</t>
+  </si>
+  <si>
+    <t>loan_account_name</t>
+  </si>
+  <si>
+    <t>loan_account_number2</t>
+  </si>
+  <si>
+    <t>loan_account_name2</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban_hyphen</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban2</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban_hyphen2</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban3</t>
+  </si>
+  <si>
+    <t>domestic_payment_bban_hyphen3</t>
+  </si>
+  <si>
+    <t>account_details_owner</t>
+  </si>
+  <si>
+    <t>account_details_owner2</t>
+  </si>
+  <si>
+    <t>cards_item_debit_card_name</t>
+  </si>
+  <si>
+    <t>cards_item_debit_card_number</t>
+  </si>
+  <si>
+    <t>cards_item_credit_card_name</t>
+  </si>
+  <si>
+    <t>cards_item_credit_card_number</t>
+  </si>
+  <si>
+    <t>auth_personal_account_number</t>
+  </si>
+  <si>
+    <t>Osir ANOEV</t>
+  </si>
+  <si>
+    <t>https://uat.dbp.nlb.si/web-retail/login</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>uat</t>
+  </si>
+  <si>
+    <t>9032033075822</t>
+  </si>
+  <si>
+    <t>Oročeni depozit</t>
+  </si>
+  <si>
+    <t>9032023653356</t>
+  </si>
+  <si>
+    <t>9032032968203</t>
+  </si>
+  <si>
+    <t>15. 1. 2016</t>
+  </si>
+  <si>
+    <t>15. 1. 2028</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Tekući račun</t>
+  </si>
+  <si>
+    <t>205-9001001027335-67</t>
+  </si>
+  <si>
+    <t>205900100102733567</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0388 8377 30</t>
+  </si>
+  <si>
+    <t>Devizni platni račun</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0918 7915 07</t>
+  </si>
+  <si>
+    <t>9011001198909</t>
+  </si>
+  <si>
+    <t>A vista depozitni račun</t>
+  </si>
+  <si>
+    <t>9011002281168</t>
+  </si>
+  <si>
+    <t>Naknada za TR</t>
+  </si>
+  <si>
+    <t>Visa revolving card</t>
+  </si>
+  <si>
+    <t>4176 **** **** 2688</t>
+  </si>
+  <si>
+    <t>Visa prepaid</t>
+  </si>
+  <si>
+    <t>4313 **** **** 5309</t>
+  </si>
+  <si>
+    <t>0049034095794</t>
+  </si>
+  <si>
+    <t>Gotovinski kredit</t>
+  </si>
+  <si>
+    <t>0049005022648</t>
+  </si>
+  <si>
+    <t>Stambeni kredit</t>
+  </si>
+  <si>
+    <t>340000003253595464</t>
+  </si>
+  <si>
+    <t>340-0000032535954-64</t>
+  </si>
+  <si>
+    <t>265111031234567824</t>
+  </si>
+  <si>
+    <t>265-1110312345678-24</t>
+  </si>
+  <si>
+    <t>170000000000077226</t>
+  </si>
+  <si>
+    <t>170-0000000000772-26</t>
+  </si>
+  <si>
+    <t>SLAVOJKA MILIVOJEVIĆ</t>
+  </si>
+  <si>
+    <t>Visa PayWave - STOJKA PEŠIĆ</t>
+  </si>
+  <si>
+    <t>4381********5007</t>
+  </si>
+  <si>
+    <t>Visa PrePaid - STOJKA PEŠIĆ</t>
+  </si>
+  <si>
+    <t>4313********0619</t>
+  </si>
+  <si>
+    <t>205-9001005222221-92</t>
+  </si>
+  <si>
+    <t>Enil ČIĆVI</t>
+  </si>
+  <si>
+    <t>15. 1. 2017</t>
+  </si>
+  <si>
+    <t>15. 1. 2029</t>
+  </si>
+  <si>
+    <t>Aor IĆVR</t>
+  </si>
+  <si>
+    <t>15. 1. 2018</t>
+  </si>
+  <si>
+    <t>15. 1. 2030</t>
+  </si>
+  <si>
+    <t>Drre ĆEVMI</t>
+  </si>
+  <si>
+    <t>15. 1. 2019</t>
+  </si>
+  <si>
+    <t>15. 1. 2031</t>
+  </si>
+  <si>
+    <t>Jail ĆEVGIMILĆ</t>
+  </si>
+  <si>
+    <t>15. 1. 2020</t>
+  </si>
+  <si>
+    <t>15. 1. 2032</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,16 +349,40 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -550,18 +522,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -876,153 +842,168 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1033,12 +1014,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1344,150 +1325,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BI5"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="4"/>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="6" width="15.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="23.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="17.8857142857143" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="13" width="29" customWidth="1"/>
-    <col min="15" max="15" width="23.2857142857143" customWidth="1"/>
-    <col min="16" max="17" width="19" customWidth="1"/>
-    <col min="18" max="18" width="24.4285714285714" customWidth="1"/>
-    <col min="19" max="20" width="36.6666666666667" customWidth="1"/>
-    <col min="21" max="21" width="23.2857142857143" customWidth="1"/>
-    <col min="22" max="26" width="28" customWidth="1"/>
-    <col min="27" max="27" width="26.7142857142857" customWidth="1"/>
-    <col min="28" max="28" width="37.8571428571429" customWidth="1"/>
-    <col min="29" max="29" width="36.5714285714286" customWidth="1"/>
-    <col min="30" max="30" width="23.2857142857143" customWidth="1"/>
-    <col min="31" max="31" width="16.8571428571429" customWidth="1"/>
-    <col min="33" max="33" width="23.2857142857143" customWidth="1"/>
-    <col min="34" max="36" width="34.5714285714286" customWidth="1"/>
-    <col min="37" max="38" width="27.8571428571429" customWidth="1"/>
-    <col min="39" max="39" width="26.5714285714286" customWidth="1"/>
-    <col min="40" max="40" width="42.1428571428571" customWidth="1"/>
-    <col min="41" max="41" width="25" customWidth="1"/>
-    <col min="42" max="42" width="30.4285714285714" customWidth="1"/>
-    <col min="43" max="43" width="29.1428571428571" customWidth="1"/>
-    <col min="44" max="44" width="23.2857142857143" customWidth="1"/>
-    <col min="45" max="45" width="38.1428571428571" customWidth="1"/>
-    <col min="46" max="46" width="29" customWidth="1"/>
-    <col min="47" max="47" width="23.7142857142857" customWidth="1"/>
-    <col min="48" max="48" width="25.7142857142857" customWidth="1"/>
-    <col min="49" max="49" width="25.4285714285714" customWidth="1"/>
-    <col min="50" max="50" width="32.7142857142857" customWidth="1"/>
-    <col min="51" max="51" width="38.5714285714286" customWidth="1"/>
-    <col min="52" max="52" width="41.7142857142857" customWidth="1"/>
-    <col min="53" max="54" width="27" customWidth="1"/>
-    <col min="55" max="55" width="27.8571428571429" customWidth="1"/>
-    <col min="56" max="56" width="38.7142857142857" customWidth="1"/>
-    <col min="57" max="57" width="28.1428571428571" customWidth="1"/>
-    <col min="58" max="59" width="23.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="35.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="5" max="5" width="22.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="19.1111111111111" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="19.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="19.1111111111111" customWidth="1"/>
+    <col min="11" max="11" width="38.7777777777778" customWidth="1"/>
+    <col min="12" max="12" width="40.1111111111111" customWidth="1"/>
+    <col min="13" max="14" width="33.8888888888889" customWidth="1"/>
+    <col min="15" max="15" width="28.8888888888889" customWidth="1"/>
+    <col min="16" max="17" width="30.4259259259259" style="1" customWidth="1"/>
+    <col min="18" max="18" width="37.8888888888889" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.8888888888889" style="1" customWidth="1"/>
+    <col min="20" max="20" width="30.4259259259259" style="1" customWidth="1"/>
+    <col min="21" max="21" width="29.6666666666667" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22.8888888888889" style="1" customWidth="1"/>
+    <col min="23" max="23" width="24.6666666666667" style="1" customWidth="1"/>
+    <col min="24" max="24" width="22.8888888888889" style="1" customWidth="1"/>
+    <col min="25" max="26" width="24.6666666666667" style="1" customWidth="1"/>
+    <col min="27" max="30" width="33.2222222222222" style="1" customWidth="1"/>
+    <col min="31" max="31" width="21.2222222222222" style="1" customWidth="1"/>
+    <col min="32" max="32" width="19.4444444444444" style="1" customWidth="1"/>
+    <col min="33" max="33" width="22.4444444444444" style="1" customWidth="1"/>
+    <col min="34" max="34" width="19.4444444444444" style="1" customWidth="1"/>
+    <col min="35" max="35" width="23.7777777777778" customWidth="1"/>
+    <col min="36" max="36" width="31.5555555555556" customWidth="1"/>
+    <col min="37" max="37" width="23.7777777777778" customWidth="1"/>
+    <col min="38" max="38" width="31.5555555555556" customWidth="1"/>
+    <col min="39" max="39" width="23.7777777777778" customWidth="1"/>
+    <col min="40" max="40" width="31.5555555555556" customWidth="1"/>
+    <col min="41" max="42" width="22.1111111111111" customWidth="1"/>
+    <col min="43" max="44" width="27.8888888888889" customWidth="1"/>
+    <col min="45" max="45" width="31.7777777777778" customWidth="1"/>
+    <col min="46" max="46" width="27.8888888888889" customWidth="1"/>
+    <col min="47" max="47" width="27.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61">
-      <c r="A1" t="s">
+    <row r="1" customFormat="1" spans="1:47">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
@@ -1529,252 +1511,1017 @@
       <c r="AU1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+    </row>
+    <row r="2" customFormat="1" spans="1:47">
+      <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="B2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="C2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="D2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="E2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="F2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="G2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="H2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="J2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="L2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="M2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="N2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="O2" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>60</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="2" ht="14" customHeight="1" spans="1:61">
-      <c r="A2">
-        <v>1379</v>
-      </c>
-      <c r="B2">
-        <v>2222</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="3" customFormat="1" spans="1:47">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="T3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="U3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F2" t="s">
+      <c r="V3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G2" t="s">
+      <c r="W3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H2" t="s">
+      <c r="X3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="Y3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="AA3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="AB3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="AC3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M2" t="s">
+      <c r="AD3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" t="s">
+      <c r="AE3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="O2" t="s">
+      <c r="AF3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="AG3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AH3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:47">
+      <c r="A4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="R2" t="s">
+      <c r="W4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="X4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AC4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AI4" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AJ4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AK4" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AL4" t="s">
         <v>79</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AM4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AN4" t="s">
         <v>81</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AO4" t="s">
         <v>82</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AP4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AR4" t="s">
         <v>84</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AS4" t="s">
         <v>85</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AT4" t="s">
         <v>86</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AU4" t="s">
         <v>87</v>
       </c>
-      <c r="AG2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM2" t="s">
+    </row>
+    <row r="5" customFormat="1" spans="1:47">
+      <c r="A5" t="s">
         <v>94</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="L5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="M5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AI5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AJ5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:47">
+      <c r="A6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="L6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AU2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AV2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AX2" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AY2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD2" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>114</v>
+      <c r="M6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK6" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3">
-        <v>1379</v>
+    <row r="7" s="1" customFormat="1" spans="1:47">
+      <c r="A7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5">
-        <v>1379</v>
+    <row r="8" s="1" customFormat="1" spans="1:47">
+      <c r="A8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="LUKA.SAJEVIC@NLB.SI" tooltip="mailto:LUKA.SAJEVIC@NLB.SI"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B5" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B6" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B7" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B8" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/testdata/configurationUAT/data.xlsx
+++ b/testdata/configurationUAT/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="15503" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="102">
   <si>
     <t>username</t>
   </si>
@@ -170,6 +170,9 @@
     <t>auth_personal_account_number</t>
   </si>
   <si>
+    <t>auth_personal_account_owner_name</t>
+  </si>
+  <si>
     <t>Osir ANOEV</t>
   </si>
   <si>
@@ -275,7 +278,7 @@
     <t>170-0000000000772-26</t>
   </si>
   <si>
-    <t>SLAVOJKA MILIVOJEVIĆ</t>
+    <t>STOJKA PEŠIĆ</t>
   </si>
   <si>
     <t>Visa PayWave - STOJKA PEŠIĆ</t>
@@ -291,6 +294,9 @@
   </si>
   <si>
     <t>205-9001005222221-92</t>
+  </si>
+  <si>
+    <t>MILENKA AĆIMOVIĆ</t>
   </si>
   <si>
     <t>Enil ČIĆVI</t>
@@ -1325,15 +1331,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU8"/>
-  <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:AV9"/>
+  <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="35.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="7.75" customWidth="1"/>
     <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="22.4444444444444" customWidth="1"/>
-    <col min="6" max="6" width="19.1111111111111" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1111111111111" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="19.1111111111111" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
@@ -1342,20 +1348,20 @@
     <col min="12" max="12" width="40.1111111111111" customWidth="1"/>
     <col min="13" max="14" width="33.8888888888889" customWidth="1"/>
     <col min="15" max="15" width="28.8888888888889" customWidth="1"/>
-    <col min="16" max="17" width="30.4259259259259" style="1" customWidth="1"/>
-    <col min="18" max="18" width="37.8888888888889" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.8888888888889" style="1" customWidth="1"/>
-    <col min="20" max="20" width="30.4259259259259" style="1" customWidth="1"/>
-    <col min="21" max="21" width="29.6666666666667" style="1" customWidth="1"/>
-    <col min="22" max="22" width="22.8888888888889" style="1" customWidth="1"/>
-    <col min="23" max="23" width="24.6666666666667" style="1" customWidth="1"/>
-    <col min="24" max="24" width="22.8888888888889" style="1" customWidth="1"/>
-    <col min="25" max="26" width="24.6666666666667" style="1" customWidth="1"/>
-    <col min="27" max="30" width="33.2222222222222" style="1" customWidth="1"/>
-    <col min="31" max="31" width="21.2222222222222" style="1" customWidth="1"/>
-    <col min="32" max="32" width="19.4444444444444" style="1" customWidth="1"/>
-    <col min="33" max="33" width="22.4444444444444" style="1" customWidth="1"/>
-    <col min="34" max="34" width="19.4444444444444" style="1" customWidth="1"/>
+    <col min="16" max="17" width="30.4259259259259" customWidth="1"/>
+    <col min="18" max="18" width="37.8888888888889" customWidth="1"/>
+    <col min="19" max="19" width="27.8888888888889" customWidth="1"/>
+    <col min="20" max="20" width="30.4259259259259" customWidth="1"/>
+    <col min="21" max="21" width="29.6666666666667" customWidth="1"/>
+    <col min="22" max="22" width="22.8888888888889" customWidth="1"/>
+    <col min="23" max="23" width="24.6666666666667" customWidth="1"/>
+    <col min="24" max="24" width="22.8888888888889" customWidth="1"/>
+    <col min="25" max="26" width="24.6666666666667" customWidth="1"/>
+    <col min="27" max="30" width="33.2222222222222" customWidth="1"/>
+    <col min="31" max="31" width="21.2222222222222" customWidth="1"/>
+    <col min="32" max="32" width="19.4444444444444" customWidth="1"/>
+    <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
+    <col min="34" max="34" width="19.4444444444444" customWidth="1"/>
     <col min="35" max="35" width="23.7777777777778" customWidth="1"/>
     <col min="36" max="36" width="31.5555555555556" customWidth="1"/>
     <col min="37" max="37" width="23.7777777777778" customWidth="1"/>
@@ -1367,9 +1373,10 @@
     <col min="45" max="45" width="31.7777777777778" customWidth="1"/>
     <col min="46" max="46" width="27.8888888888889" customWidth="1"/>
     <col min="47" max="47" width="27.2222222222222" customWidth="1"/>
+    <col min="48" max="48" width="35.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:47">
+    <row r="1" customFormat="1" spans="1:48">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1511,1006 +1518,1176 @@
       <c r="AU1" t="s">
         <v>46</v>
       </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:47">
+    <row r="2" customFormat="1" spans="1:48">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:48">
+      <c r="A3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:48">
+      <c r="A4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="F4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="H4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:48">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="F5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="J5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="N5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R2" s="8" t="s">
+      <c r="R5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM5" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:48">
+      <c r="A6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="P6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="U6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="V6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="W6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="X6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:48">
+      <c r="A7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="W7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="Y7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AA7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AB7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AC7" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AD7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AE7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AF7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AG7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AH7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AI7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AJ7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AK7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AL7" t="s">
         <v>80</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AM7" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AN7" t="s">
         <v>82</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AO7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:48">
+      <c r="A8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN8" t="s">
         <v>82</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AO8" t="s">
         <v>83</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AP8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>84</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AR8" t="s">
         <v>85</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AS8" t="s">
         <v>86</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AT8" t="s">
         <v>87</v>
       </c>
+      <c r="AU8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="3" customFormat="1" spans="1:47">
-      <c r="A3" s="1" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:48">
+      <c r="A9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU9" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="AV9" t="s">
         <v>89</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI3" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ3" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK3" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:47">
-      <c r="A4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI4" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:47">
-      <c r="A5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI5" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM5" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:47">
-      <c r="A6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI6" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM6" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:47">
-      <c r="A7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X7" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI7" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ7" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM7" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:47">
-      <c r="A8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2522,6 +2699,7 @@
     <hyperlink ref="B6" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B7" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B8" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B9" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
